--- a/artfynd/A 24660-2025 artfynd.xlsx
+++ b/artfynd/A 24660-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63188840</v>
+        <v>63201066</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -739,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562680.1761626749</v>
+        <v>562680</v>
       </c>
       <c r="R2" t="n">
-        <v>6257733.176321578</v>
+        <v>6257733</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,19 +767,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -816,42 +801,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63202897</v>
+        <v>63201834</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205994</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Sydpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -880,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562680.1761626749</v>
+        <v>562680</v>
       </c>
       <c r="R3" t="n">
-        <v>6257733.176321578</v>
+        <v>6257733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,19 +893,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -957,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63201066</v>
+        <v>63202897</v>
       </c>
       <c r="B4" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,21 +938,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1021,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562680.1761626749</v>
+        <v>562680</v>
       </c>
       <c r="R4" t="n">
-        <v>6257733.176321578</v>
+        <v>6257733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1054,19 +1019,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-06-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1098,42 +1053,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63201834</v>
+        <v>63188840</v>
       </c>
       <c r="B5" t="n">
-        <v>57502</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205994</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pipistrellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1162,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562680.1761626749</v>
+        <v>562680</v>
       </c>
       <c r="R5" t="n">
-        <v>6257733.176321578</v>
+        <v>6257733</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,19 +1145,9 @@
           <t>2011-06-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-06-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
